--- a/job_application_forms/034_sports_industry_employment_application--job_application_forms.xlsx
+++ b/job_application_forms/034_sports_industry_employment_application--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Submitter Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Submitter Review</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Agreement</t>
+          <t>Submitter Agreement 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Submitter Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Submitter Time 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Submitter Signature 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pass',_'value':_1}</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pass', 'value': 1}</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fail',_'value':_2}</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fail', 'value': 2}</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pass',_'value':_1}</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pass', 'value': 1}</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fail',_'value':_2}</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fail', 'value': 2}</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_agree_to_submit_the_application_for_review',_'value':_1}</t>
+          <t>i_agree_to_submit_the_application_for_review</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I agree to submit the application for review', 'value': 1}</t>
+          <t>I agree to submit the application for review</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_do_not_agree_to_submit_the_application_for_review',_'value':_2}</t>
+          <t>i_do_not_agree_to_submit_the_application_for_review</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I do not agree to submit the application for review', 'value': 2}</t>
+          <t>I do not agree to submit the application for review</t>
         </is>
       </c>
     </row>
